--- a/examples/result.xlsx
+++ b/examples/result.xlsx
@@ -37,7 +37,7 @@
     <t>头程运费</t>
   </si>
   <si>
-    <t>含税成本</t>
+    <t>包装成本</t>
   </si>
   <si>
     <t>佣金率</t>
@@ -67,7 +67,7 @@
     <t>建议售价</t>
   </si>
   <si>
-    <t>月供测算</t>
+    <t>毛利投产比</t>
   </si>
   <si>
     <t>是否达标</t>
@@ -502,7 +502,7 @@
         <v>24</v>
       </c>
       <c r="E2">
-        <v>42.5</v>
+        <v>36</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -511,7 +511,7 @@
         <v>25</v>
       </c>
       <c r="H2">
-        <v>48.03</v>
+        <v>4.32</v>
       </c>
       <c r="I2">
         <v>0.08</v>
@@ -520,7 +520,7 @@
         <v>8</v>
       </c>
       <c r="K2">
-        <v>0.78</v>
+        <v>31.12</v>
       </c>
       <c r="L2">
         <v>99</v>
@@ -529,10 +529,10 @@
         <v>7.92</v>
       </c>
       <c r="N2">
-        <v>82.3</v>
+        <v>51.96</v>
       </c>
       <c r="O2">
-        <v>0.8313</v>
+        <v>0.5248</v>
       </c>
       <c r="P2" t="s">
         <v>25</v>
@@ -541,7 +541,7 @@
         <v>120</v>
       </c>
       <c r="R2">
-        <v>8.52</v>
+        <v>6.5</v>
       </c>
       <c r="S2" t="s">
         <v>26</v>
@@ -561,7 +561,7 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>42.5</v>
+        <v>36</v>
       </c>
       <c r="F3">
         <v>100</v>
@@ -570,7 +570,7 @@
         <v>25</v>
       </c>
       <c r="H3">
-        <v>48.03</v>
+        <v>4.32</v>
       </c>
       <c r="I3">
         <v>0.08</v>
@@ -579,7 +579,7 @@
         <v>8</v>
       </c>
       <c r="K3">
-        <v>0.78</v>
+        <v>31.12</v>
       </c>
       <c r="L3">
         <v>99</v>
@@ -588,10 +588,10 @@
         <v>7.92</v>
       </c>
       <c r="N3">
-        <v>82.3</v>
+        <v>51.96</v>
       </c>
       <c r="O3">
-        <v>0.8313</v>
+        <v>0.5248</v>
       </c>
       <c r="P3" t="s">
         <v>25</v>
@@ -600,7 +600,7 @@
         <v>120</v>
       </c>
       <c r="R3">
-        <v>8.52</v>
+        <v>6.5</v>
       </c>
       <c r="S3" t="s">
         <v>26</v>
@@ -620,7 +620,7 @@
         <v>24</v>
       </c>
       <c r="E4">
-        <v>42.5</v>
+        <v>36</v>
       </c>
       <c r="F4">
         <v>100</v>
@@ -629,7 +629,7 @@
         <v>25</v>
       </c>
       <c r="H4">
-        <v>48.03</v>
+        <v>4.32</v>
       </c>
       <c r="I4">
         <v>0.08</v>
@@ -638,7 +638,7 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>0.78</v>
+        <v>31.12</v>
       </c>
       <c r="L4">
         <v>99</v>
@@ -647,10 +647,10 @@
         <v>7.92</v>
       </c>
       <c r="N4">
-        <v>82.3</v>
+        <v>51.96</v>
       </c>
       <c r="O4">
-        <v>0.8313</v>
+        <v>0.5248</v>
       </c>
       <c r="P4" t="s">
         <v>25</v>
@@ -659,7 +659,7 @@
         <v>120</v>
       </c>
       <c r="R4">
-        <v>8.52</v>
+        <v>6.5</v>
       </c>
       <c r="S4" t="s">
         <v>26</v>
